--- a/quizzes/sculpture-18e-niveau2.xlsx
+++ b/quizzes/sculpture-18e-niveau2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers en préparation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10968D31-9574-49FB-B188-48BF41D19B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1D7FCD-9D47-461B-B31F-67A6C4949A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="266">
   <si>
     <t>image</t>
   </si>
@@ -595,12 +595,6 @@
     <t>La Prière au jardin</t>
   </si>
   <si>
-    <t>ttps://upload.wikimedia.org/wikipedia/commons/thumb/9/98/Nymphenburg_Pantalone_VA_C153-1932.jpg/960px-Nymphenburg_Pantalone_VA_C153-1932.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Figure de Pantalone, modelée en porcelaine dure</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Statues_of_Venus_Urania_by_Fran%C3%A7ois_Gaspard_Adam-The_Marble_Hall-Interior_of_Schloss_Sanssouci.jpg/500px-Statues_of_Venus_Urania_by_Fran%C3%A7ois_Gaspard_Adam-The_Marble_Hall-Interior_of_Schloss_Sanssouci.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -815,6 +809,15 @@
   </si>
   <si>
     <t>Place Stanislas, Nancy</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Franz_Anton_Bustelli_Liebesgruppe_1756-1.jpg/1280px-Franz_Anton_Bustelli_Liebesgruppe_1756-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
+  </si>
+  <si>
+    <t>Bayerisches Nationalmuseum, Munich</t>
+  </si>
+  <si>
+    <t>L'amoureux fougueux</t>
   </si>
 </sst>
 </file>
@@ -854,7 +857,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -876,6 +879,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -939,7 +948,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -974,6 +983,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1277,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="127.28515625" customWidth="1"/>
@@ -1391,19 +1401,19 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C7" s="12">
         <v>1750</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1559,7 +1569,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
         <v>95</v>
       </c>
@@ -1576,7 +1586,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
         <v>188</v>
       </c>
@@ -1593,26 +1603,27 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6" s="16" customFormat="1">
       <c r="A19" s="8" t="s">
-        <v>191</v>
+        <v>263</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>150</v>
       </c>
       <c r="C19" s="12">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>265</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>151</v>
@@ -1621,13 +1632,13 @@
         <v>1748</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
         <v>132</v>
       </c>
@@ -1644,7 +1655,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
         <v>85</v>
       </c>
@@ -1661,43 +1672,43 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>152</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="7" t="s">
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="8" t="s">
         <v>198</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="8" t="s">
-        <v>200</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>153</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>143</v>
@@ -1709,27 +1720,27 @@
         <v>173</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>154</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
         <v>100</v>
       </c>
@@ -1746,9 +1757,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>155</v>
@@ -1757,13 +1768,13 @@
         <v>1705</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
@@ -1780,9 +1791,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:6">
       <c r="A30" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>156</v>
@@ -1794,10 +1805,10 @@
         <v>16</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
         <v>49</v>
       </c>
@@ -1814,9 +1825,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6">
       <c r="A32" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>157</v>
@@ -1828,7 +1839,7 @@
         <v>16</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1884,7 +1895,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>159</v>
@@ -1896,12 +1907,12 @@
         <v>16</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>160</v>
@@ -1910,10 +1921,10 @@
         <v>1794</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1930,7 +1941,7 @@
         <v>81</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1947,63 +1958,63 @@
         <v>110</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>161</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>162</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>163</v>
       </c>
       <c r="C42" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="E42" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>164</v>
@@ -2012,10 +2023,10 @@
         <v>1785</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2054,36 +2065,36 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>165</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>239</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C47" s="12">
         <v>1791</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2139,7 +2150,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>166</v>
@@ -2151,12 +2162,12 @@
         <v>16</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>167</v>
@@ -2165,10 +2176,10 @@
         <v>1735</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2190,7 +2201,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>144</v>
@@ -2199,10 +2210,10 @@
         <v>1710</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2224,7 +2235,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>170</v>
@@ -2236,7 +2247,7 @@
         <v>16</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2258,19 +2269,19 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>169</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2292,7 +2303,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>168</v>
@@ -2304,7 +2315,7 @@
         <v>16</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2365,30 +2376,30 @@
     <hyperlink ref="A15" r:id="rId34" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Abundance%22_by_Filippo_della_Valle_%28Florence_1698-Rome_1768%29_-_Fountain_of_Trevi_%281732-1762%29_in_Rome_%2823235744623%29.jpg/960px-%22Abundance%22_by_Filippo_della_Valle_%28Florence_1698-Rome_1768%29_-_Fountain_of_Trevi_%281732-1762%29_in_Rome_%2823235744623%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B408CFAD-C1B0-4E96-BC9E-BCB2AAEA47EC}"/>
     <hyperlink ref="A16" r:id="rId35" xr:uid="{002648C8-13D4-481B-831A-4FB57518DE24}"/>
     <hyperlink ref="A18" r:id="rId36" xr:uid="{31282AE6-86C4-4920-BABD-BEE01B4BB576}"/>
-    <hyperlink ref="A19" r:id="rId37" xr:uid="{3D6AD395-980E-4DCE-90A4-4C83673E0803}"/>
-    <hyperlink ref="A20" r:id="rId38" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Statues_of_Venus_Urania_by_Fran%C3%A7ois_Gaspard_Adam-The_Marble_Hall-Interior_of_Schloss_Sanssouci.jpg/500px-Statues_of_Venus_Urania_by_Fran%C3%A7ois_Gaspard_Adam-The_Marble_Hall-Interior_of_Schloss_Sanssouci.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EA9F8AA0-BE59-4EB1-9A45-96E4420FAD7B}"/>
-    <hyperlink ref="A23" r:id="rId39" xr:uid="{C8308364-EB34-4E31-AC19-7D034164F63C}"/>
-    <hyperlink ref="A24" r:id="rId40" xr:uid="{87EA05CD-9941-4C6A-AE05-CBB2909032E1}"/>
-    <hyperlink ref="A25" r:id="rId41" xr:uid="{AD6B5870-8AFB-4928-A3D2-AE3857083B66}"/>
-    <hyperlink ref="A28" r:id="rId42" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/23/Ca%27_Rezzonico_-_Democrito_%281705%29_-_Giuseppe_Torretti.jpg/960px-Ca%27_Rezzonico_-_Democrito_%281705%29_-_Giuseppe_Torretti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC8019F2-D195-4598-BBB7-6B7CF18B2C3A}"/>
-    <hyperlink ref="A30" r:id="rId43" xr:uid="{F566F0E4-C18F-4AD7-A0F3-6A6FF7B3AED1}"/>
-    <hyperlink ref="A26" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{03ADD225-97B2-475F-A21D-4DCDD9E4F41D}"/>
-    <hyperlink ref="A32" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/L%27Amour_essayant_une_de_ses_fl%C3%A8ches_-_Jacques_Saly_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2016.2.1_%3B_ENT_2015.4.jpg/960px-L%27Amour_essayant_une_de_ses_fl%C3%A8ches_-_Jacques_Saly_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2016.2.1_%3B_ENT_2015.4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{645159E7-D216-4653-9D1F-4C8FCF684840}"/>
-    <hyperlink ref="A36" r:id="rId46" xr:uid="{725ACB3F-C559-4542-858A-AE6A70813F34}"/>
-    <hyperlink ref="A37" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Jean-Jacques_Rousseau_observant_les_premiers_pas_de_l%E2%80%99enfance%2C_ou_l%27%C3%A9ducation_d%27Emile%2C_S3314%2818%29.jpg/960px-Jean-Jacques_Rousseau_observant_les_premiers_pas_de_l%E2%80%99enfance%2C_ou_l%27%C3%A9ducation_d%27Emile%2C_S3314%2818%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E1B0E1A-44EA-40C9-86DA-FE6092D7EC29}"/>
-    <hyperlink ref="A40" r:id="rId48" xr:uid="{54E9AB98-2C9F-46E0-94B9-1DCF896F4F3E}"/>
-    <hyperlink ref="A41" r:id="rId49" xr:uid="{2291B182-7276-4FC3-9BE1-561F0AC4848F}"/>
-    <hyperlink ref="A42" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/J._J._Kaendler_Terrine_aus_dem_Schwanenservice%2C_1738%2C_Lustheim-1.jpg/960px-J._J._Kaendler_Terrine_aus_dem_Schwanenservice%2C_1738%2C_Lustheim-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7907AE22-CA59-40BC-A2BE-DA1DF2B8CB19}"/>
-    <hyperlink ref="A43" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/8/8a/Apotheosis_of_Homer_vase%2C_John_Flaxman_designer%2C_Josiah_Wedgwood_Factory%2C_Staffordshire%2C_England%2C_designed_c._1785%2C_made_c._1870%2C_jasperware_-_Dallas_Museum_of_Art_-_DSC05154.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{BC3E79D5-E309-46E9-820F-CDC6C209D849}"/>
-    <hyperlink ref="A46" r:id="rId52" xr:uid="{787AC4B9-5747-41B3-BA24-F9FF411E7EAF}"/>
-    <hyperlink ref="A47" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/La_Raison_sous_les_traits_d%27Apollon_foulant_%C3%A0_ses_pieds_le_Despotisme_et_la_Superstition%2C_S26.jpg/1280px-La_Raison_sous_les_traits_d%27Apollon_foulant_%C3%A0_ses_pieds_le_Despotisme_et_la_Superstition%2C_S26.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{972D212D-8DBC-48D2-B671-CC0B8938A5BC}"/>
-    <hyperlink ref="A51" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg/1280px-Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B2C00F60-C55A-429D-A96E-B89E89896215}"/>
-    <hyperlink ref="A52" r:id="rId55" xr:uid="{1D682AE1-8521-4A7D-971A-5C5A412A9FDF}"/>
-    <hyperlink ref="A54" r:id="rId56" xr:uid="{9A64873F-F532-42D9-A188-37C501119917}"/>
-    <hyperlink ref="A56" r:id="rId57" xr:uid="{024A23F9-4676-46D0-83D0-0C4F4D5E5462}"/>
-    <hyperlink ref="A58" r:id="rId58" xr:uid="{43E76E16-0D4F-48CF-9FAA-EBE9DC327F84}"/>
-    <hyperlink ref="A60" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg/960px-Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8C33DE62-677A-417F-8C99-A34888DEC45E}"/>
-    <hyperlink ref="A7" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/cf/Nancy_%28Meurthe-et-Moselle%29_-_Place_Stanislas_-_Fontaine_d%27Amphitrite_et_portiques_de_Jean_Lamour_%2839820576293%29.jpg/960px-Nancy_%28Meurthe-et-Moselle%29_-_Place_Stanislas_-_Fontaine_d%27Amphitrite_et_portiques_de_Jean_Lamour_%2839820576293%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6EC27795-BCCC-4A01-9C08-07CA96D25E90}"/>
+    <hyperlink ref="A20" r:id="rId37" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Statues_of_Venus_Urania_by_Fran%C3%A7ois_Gaspard_Adam-The_Marble_Hall-Interior_of_Schloss_Sanssouci.jpg/500px-Statues_of_Venus_Urania_by_Fran%C3%A7ois_Gaspard_Adam-The_Marble_Hall-Interior_of_Schloss_Sanssouci.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EA9F8AA0-BE59-4EB1-9A45-96E4420FAD7B}"/>
+    <hyperlink ref="A23" r:id="rId38" xr:uid="{C8308364-EB34-4E31-AC19-7D034164F63C}"/>
+    <hyperlink ref="A24" r:id="rId39" xr:uid="{87EA05CD-9941-4C6A-AE05-CBB2909032E1}"/>
+    <hyperlink ref="A25" r:id="rId40" xr:uid="{AD6B5870-8AFB-4928-A3D2-AE3857083B66}"/>
+    <hyperlink ref="A28" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/23/Ca%27_Rezzonico_-_Democrito_%281705%29_-_Giuseppe_Torretti.jpg/960px-Ca%27_Rezzonico_-_Democrito_%281705%29_-_Giuseppe_Torretti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC8019F2-D195-4598-BBB7-6B7CF18B2C3A}"/>
+    <hyperlink ref="A30" r:id="rId42" xr:uid="{F566F0E4-C18F-4AD7-A0F3-6A6FF7B3AED1}"/>
+    <hyperlink ref="A26" r:id="rId43" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{03ADD225-97B2-475F-A21D-4DCDD9E4F41D}"/>
+    <hyperlink ref="A32" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/L%27Amour_essayant_une_de_ses_fl%C3%A8ches_-_Jacques_Saly_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2016.2.1_%3B_ENT_2015.4.jpg/960px-L%27Amour_essayant_une_de_ses_fl%C3%A8ches_-_Jacques_Saly_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2016.2.1_%3B_ENT_2015.4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{645159E7-D216-4653-9D1F-4C8FCF684840}"/>
+    <hyperlink ref="A36" r:id="rId45" xr:uid="{725ACB3F-C559-4542-858A-AE6A70813F34}"/>
+    <hyperlink ref="A37" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Jean-Jacques_Rousseau_observant_les_premiers_pas_de_l%E2%80%99enfance%2C_ou_l%27%C3%A9ducation_d%27Emile%2C_S3314%2818%29.jpg/960px-Jean-Jacques_Rousseau_observant_les_premiers_pas_de_l%E2%80%99enfance%2C_ou_l%27%C3%A9ducation_d%27Emile%2C_S3314%2818%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E1B0E1A-44EA-40C9-86DA-FE6092D7EC29}"/>
+    <hyperlink ref="A40" r:id="rId47" xr:uid="{54E9AB98-2C9F-46E0-94B9-1DCF896F4F3E}"/>
+    <hyperlink ref="A41" r:id="rId48" xr:uid="{2291B182-7276-4FC3-9BE1-561F0AC4848F}"/>
+    <hyperlink ref="A42" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/J._J._Kaendler_Terrine_aus_dem_Schwanenservice%2C_1738%2C_Lustheim-1.jpg/960px-J._J._Kaendler_Terrine_aus_dem_Schwanenservice%2C_1738%2C_Lustheim-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7907AE22-CA59-40BC-A2BE-DA1DF2B8CB19}"/>
+    <hyperlink ref="A43" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/8/8a/Apotheosis_of_Homer_vase%2C_John_Flaxman_designer%2C_Josiah_Wedgwood_Factory%2C_Staffordshire%2C_England%2C_designed_c._1785%2C_made_c._1870%2C_jasperware_-_Dallas_Museum_of_Art_-_DSC05154.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{BC3E79D5-E309-46E9-820F-CDC6C209D849}"/>
+    <hyperlink ref="A46" r:id="rId51" xr:uid="{787AC4B9-5747-41B3-BA24-F9FF411E7EAF}"/>
+    <hyperlink ref="A47" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/La_Raison_sous_les_traits_d%27Apollon_foulant_%C3%A0_ses_pieds_le_Despotisme_et_la_Superstition%2C_S26.jpg/1280px-La_Raison_sous_les_traits_d%27Apollon_foulant_%C3%A0_ses_pieds_le_Despotisme_et_la_Superstition%2C_S26.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{972D212D-8DBC-48D2-B671-CC0B8938A5BC}"/>
+    <hyperlink ref="A51" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg/1280px-Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B2C00F60-C55A-429D-A96E-B89E89896215}"/>
+    <hyperlink ref="A52" r:id="rId54" xr:uid="{1D682AE1-8521-4A7D-971A-5C5A412A9FDF}"/>
+    <hyperlink ref="A54" r:id="rId55" xr:uid="{9A64873F-F532-42D9-A188-37C501119917}"/>
+    <hyperlink ref="A56" r:id="rId56" xr:uid="{024A23F9-4676-46D0-83D0-0C4F4D5E5462}"/>
+    <hyperlink ref="A58" r:id="rId57" xr:uid="{43E76E16-0D4F-48CF-9FAA-EBE9DC327F84}"/>
+    <hyperlink ref="A60" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg/960px-Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8C33DE62-677A-417F-8C99-A34888DEC45E}"/>
+    <hyperlink ref="A7" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/cf/Nancy_%28Meurthe-et-Moselle%29_-_Place_Stanislas_-_Fontaine_d%27Amphitrite_et_portiques_de_Jean_Lamour_%2839820576293%29.jpg/960px-Nancy_%28Meurthe-et-Moselle%29_-_Place_Stanislas_-_Fontaine_d%27Amphitrite_et_portiques_de_Jean_Lamour_%2839820576293%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6EC27795-BCCC-4A01-9C08-07CA96D25E90}"/>
+    <hyperlink ref="A19" r:id="rId60" xr:uid="{7BA54018-1CCA-49F4-AD2D-CEC9D3192285}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
